--- a/data/Buff.xlsx
+++ b/data/Buff.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -82,12 +82,6 @@
     <t>提高每发子弹的伤害</t>
   </si>
   <si>
-    <t>分裂射击</t>
-  </si>
-  <si>
-    <t>每次射击额外发射一枚子弹</t>
-  </si>
-  <si>
     <t>弹性子弹</t>
   </si>
   <si>
@@ -98,12 +92,6 @@
   </si>
   <si>
     <t>显著提高子弹伤害，并提高暴击几率</t>
-  </si>
-  <si>
-    <t>弹幕扩容</t>
-  </si>
-  <si>
-    <t>一次射击增加轮数</t>
   </si>
   <si>
     <t>要害射击</t>
@@ -1418,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1513,76 +1501,76 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="14.4" spans="1:5">
       <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="13">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="14.4" spans="1:5">
       <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="13">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="14.4" spans="1:5">
       <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="13">
-        <v>2</v>
-      </c>
-      <c r="E8" s="13">
-        <v>30</v>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="14.4" spans="1:5">
       <c r="A9" s="13">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="13">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13">
-        <v>20</v>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="14.4" spans="1:5">
-      <c r="A10">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -1609,14 +1597,14 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="14.4" spans="1:5">
-      <c r="A12">
+      <c r="A12" s="13">
         <v>8</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -1626,10 +1614,10 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="14.4" spans="1:5">
@@ -1650,7 +1638,7 @@
       </c>
     </row>
     <row r="14" ht="14.4" spans="1:5">
-      <c r="A14">
+      <c r="A14" s="13">
         <v>10</v>
       </c>
       <c r="B14" s="15" t="s">
@@ -1660,51 +1648,17 @@
         <v>33</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="15" ht="14.4" spans="1:5">
-      <c r="A15" s="13">
-        <v>11</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="14.4" spans="1:5">
-      <c r="A16">
-        <v>12</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
+    <row r="15" spans="1:5">
+      <c r="A15" s="13"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="13"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
